--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,305 +661,185 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -969,19 +849,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -991,212 +871,212 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>2.20</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>3.40</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1206,46 +1086,46 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1255,24 +1135,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1284,51 +1164,51 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1338,19 +1218,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1360,98 +1240,318 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>4.75</t>
         </is>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
@@ -656,29 +656,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -688,180 +700,276 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>4.75</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>3.40</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -871,687 +979,467 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
         <is>
           <t>4.75</t>
         </is>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -668,29 +668,17 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
+          <t>8j9FTL56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -700,315 +688,219 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1018,430 +910,628 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>4.75</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>5.50</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,117 +448,117 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>1.57</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,63 +573,63 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,24 +661,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -688,7 +700,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -698,7 +710,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -708,7 +720,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -718,7 +730,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -728,7 +740,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -738,7 +750,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -748,7 +760,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -758,7 +770,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -768,430 +780,406 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>pWQ6LC1N</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>1.57</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>hzeTFV7m</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1201,107 +1189,107 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1311,227 +1299,29 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>GEugARyP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
           <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>5.50</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,860 +448,980 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>19.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9.15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4.41</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>rRQ6H30k</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>dUjtW2Fr</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>MFnpCm7C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>UsklUtpe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>ddFjPf2b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>Sh9BS8ig</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>dAfPwfHi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>pWQ6LC1N</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>jiUEFsV1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>dY0SOQjI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>hO8aNYWA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>vDA9yPiL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>hzeTFV7m</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>Q9rcSKE7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>zJCJQnM5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>QkntzCGG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>Wn71woN8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EkqxE9x0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>GEugARyP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>U32wGjPp</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>hGzqjO6E</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>OrHrRGXo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>WQF2UUMt</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>rkazN4LU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>hxlYyYo4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1311,227 +1431,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>5.50</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -673,17 +673,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -739,17 +739,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -761,17 +761,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.65</t>
         </is>
       </c>
     </row>
@@ -805,17 +805,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.30</t>
         </is>
       </c>
     </row>
@@ -827,17 +827,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -871,567 +871,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rRQ6H30k</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>dUjtW2Fr</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>MFnpCm7C</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>UsklUtpe</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddFjPf2b</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Sh9BS8ig</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>dAfPwfHi</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>pWQ6LC1N</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>jiUEFsV1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>dY0SOQjI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>hO8aNYWA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>vDA9yPiL</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>hzeTFV7m</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Q9rcSKE7</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>zJCJQnM5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>QkntzCGG</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Wn71woN8</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkqxE9x0</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>GEugARyP</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>U32wGjPp</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>hGzqjO6E</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>OrHrRGXo</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>WQF2UUMt</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>rkazN4LU</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>hxlYyYo4</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2.10</t>
+          <t>1.72</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>21.00</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -585,303 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>1.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6.20</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>5.80</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.72</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,154 +448,286 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.73</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,286 +448,220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>4.75</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.70</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>3.50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -651,17 +651,193 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,396 +448,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2kGeEq1e</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2TvL16Hk</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.00</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>4.20</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.83</t>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.10</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
@@ -662,6 +662,226 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.80</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,440 +448,44 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2kGeEq1e</t>
+          <t>AFJ3CNV7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2TvL16Hk</t>
+          <t>Of1jzRNE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>beYTapn2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>jkLFNmv9</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>AiyHLR8L</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tzSnG5Wr</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Wplk7SgS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>AVat9lPF</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AFJ3CNV7</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Of1jzRNE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>C0axT3Xo</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>d8abY4hR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>pYXoP0FD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>xtzXn47K</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dQG3srVs</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Q58Kw0U6</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W2BSyvaJ</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OIqwRMp1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>GhtVSrGl</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>UwFBuMaf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3.80</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,34 +458,430 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.00</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,227 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>4.75</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>5.00</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,44 +448,440 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>8MkyzwoT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.30</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>2.63</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -639,249 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SQM1jbV9</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bFdtqGNq</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>l0Zi1FqS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.30</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,198 +448,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>KnvLwLo4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.88</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,352 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.25</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,352 +448,264 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,264 +448,440 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>3.00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>4.50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -519,12 +519,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.33</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,51 +448,51 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>1.30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -508,380 +508,6 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ShJjaSDs</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>SSZaQ4Ct</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2ot8gOsJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KMCY9qSa</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>v5b6XwQN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ABRGMMB5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>rPPOK0tI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>viJXIvBU</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zypxSHmo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>rw5cZaeB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EcDtwrdn</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zD1kyMQb</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>EJlHkLuh</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>EqY7Orsg</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3.30</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,440 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3.00</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>17.00</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>4.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -651,237 +651,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3.25</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,78 +448,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>WIs9mjGL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>MqhPmaA4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>lb85TUOk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>rc1ER8g2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,41 +529,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>21YvrUwq</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17.00</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>OGMmt88e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,95 +573,315 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>EJ4unbdE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>4.10</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0d4cBEPP</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KK9ggF3s</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hY71igYg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CEnSxfJ0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>2.90</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.30</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2.60</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.63</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -656,232 +656,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nX2mpxRQ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>YTzyyYmD</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>K0RAmBXI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0d4cBEPP</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HqKvGll</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0zTMbytK</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KK9ggF3s</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hY71igYg</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>CzO2kX26</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CEnSxfJ0</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.30</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -448,220 +448,220 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/england/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>2.63</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,171 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EubK3NNG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cl3y4WHa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p21q2AnC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WveT5hmm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v3JHq2Wp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.38</t>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69B375Oi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>A7iT11hT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5.50</t>
         </is>
       </c>
     </row>
